--- a/ig/improve-doc/ValueSet-JDV-J35-SpecialisationDePriseEnCharge-ROR.xlsx
+++ b/ig/improve-doc/ValueSet-JDV-J35-SpecialisationDePriseEnCharge-ROR.xlsx
@@ -505,7 +505,7 @@
     <t>https://mos.esante.gouv.fr/NOS/TRE_R245-SpecialisationDePriseEnCharge/FHIR/TRE-R245-SpecialisationDePriseEnCharge</t>
   </si>
   <si>
-    <t>68</t>
+    <t>068</t>
   </si>
   <si>
     <t>Troubles cognitifs ou du comportement et de la relation affective dus à une lésion cérébrale acquise</t>
